--- a/data/pending_orders.xlsx
+++ b/data/pending_orders.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Actual pending as on today" sheetId="23" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Actual pending as on today'!$3:$107</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Actual pending as on today'!$3:$100</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="646" uniqueCount="304">
   <si>
     <t>Yuno Packaging Pvt. Ltd.</t>
   </si>
@@ -944,66 +944,6 @@
   </si>
   <si>
     <t>2094118 - CAR SERTRAL 100MG TAB 3X10S AMAR NL 2089</t>
-  </si>
-  <si>
-    <t>BN-2627/1354</t>
-  </si>
-  <si>
-    <t>FP2/2627/POS/PPM/00464</t>
-  </si>
-  <si>
-    <t> 24/08/2026</t>
-  </si>
-  <si>
-    <t>P1014/01</t>
-  </si>
-  <si>
-    <t>P1014/01 - CETIRIZINE 10MG TABS CARTON 50S PACK</t>
-  </si>
-  <si>
-    <t>BN-2627/1355</t>
-  </si>
-  <si>
-    <t>1050730 - PCT-APX-DOXY 50MG-1X25 S-ARROTEX,AUS-R1</t>
-  </si>
-  <si>
-    <t>BN-2627/1356</t>
-  </si>
-  <si>
-    <t>1050204 - PCT-VALACICLOVIR-500MG-3X10S-WAGNER</t>
-  </si>
-  <si>
-    <t>BN-2627/1359</t>
-  </si>
-  <si>
-    <t>2077975 - PRINTED BLISTER CARTON FOR PANTROX 40 (PANTOPRAZOLE 40MG TABLETS) 6X10S SAUDI AMAROX SAUDI ARABIA</t>
-  </si>
-  <si>
-    <t>BN-2627/1360</t>
-  </si>
-  <si>
-    <t>SHILPA MEDICARE LIMITED</t>
-  </si>
-  <si>
-    <t>4200353 - PLAIN CARTON 87 X 70 X 32 MM (LXWXH) TUCKIN FLAPS</t>
-  </si>
-  <si>
-    <t>BN-2627/1365</t>
-  </si>
-  <si>
-    <t>1312001515-01</t>
-  </si>
-  <si>
-    <t>1312001515-01 - CTN PHYTONA EMU,USP10MG/ML US XM</t>
-  </si>
-  <si>
-    <t>BN-2627/1366</t>
-  </si>
-  <si>
-    <t>1312002110-00</t>
-  </si>
-  <si>
-    <t>1312002110-00 - CTN DALBAVANCIN 500MG/VIAL US GNP</t>
   </si>
 </sst>
 </file>
@@ -2397,7 +2337,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:XFD1048381"/>
+  <dimension ref="A1:XFD1048374"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="14.1428571428571" style="3" customWidth="1"/>
@@ -9197,7 +9137,7 @@
       <c r="XFC96" s="26"/>
       <c r="XFD96" s="26"/>
     </row>
-    <row r="97" s="1" customFormat="1" ht="14.1" customHeight="1" spans="1:25 16372:16384">
+    <row r="97" s="1" customFormat="1" ht="14.1" customHeight="1" spans="1:20 16374:16384">
       <c r="A97" s="24" t="s">
         <v>295</v>
       </c>
@@ -9262,7 +9202,7 @@
       <c r="XFC97" s="26"/>
       <c r="XFD97" s="26"/>
     </row>
-    <row r="98" s="1" customFormat="1" ht="14.1" customHeight="1" spans="1:25 16372:16384">
+    <row r="98" s="1" customFormat="1" ht="14.1" customHeight="1" spans="1:20 16374:16384">
       <c r="A98" s="24" t="s">
         <v>298</v>
       </c>
@@ -9327,7 +9267,7 @@
       <c r="XFC98" s="26"/>
       <c r="XFD98" s="26"/>
     </row>
-    <row r="99" s="1" customFormat="1" ht="14.1" customHeight="1" spans="1:25 16372:16384">
+    <row r="99" s="1" customFormat="1" ht="14.1" customHeight="1" spans="1:20 16374:16384">
       <c r="A99" s="24" t="s">
         <v>300</v>
       </c>
@@ -9392,7 +9332,7 @@
       <c r="XFC99" s="24"/>
       <c r="XFD99" s="25"/>
     </row>
-    <row r="100" s="1" customFormat="1" ht="14.1" customHeight="1" spans="1:25 16372:16384">
+    <row r="100" s="1" customFormat="1" ht="14.1" customHeight="1" spans="1:20 16374:16384">
       <c r="A100" s="24" t="s">
         <v>302</v>
       </c>
@@ -9457,505 +9397,94 @@
       <c r="XFC100" s="24"/>
       <c r="XFD100" s="25"/>
     </row>
-    <row r="101" s="1" customFormat="1" ht="14.1" customHeight="1" spans="1:25 16372:16384">
-      <c r="A101" s="24" t="s">
-        <v>304</v>
-      </c>
-      <c r="B101" s="25">
-        <v>46259</v>
-      </c>
-      <c r="C101" s="26" t="s">
-        <v>305</v>
-      </c>
-      <c r="D101" s="26" t="s">
-        <v>306</v>
-      </c>
-      <c r="E101" s="27" t="s">
-        <v>178</v>
-      </c>
-      <c r="F101" s="28" t="s">
-        <v>209</v>
-      </c>
-      <c r="G101" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="H101" s="29" t="s">
-        <v>307</v>
-      </c>
-      <c r="I101" s="29" t="s">
-        <v>308</v>
-      </c>
-      <c r="J101" s="24">
-        <v>15000</v>
-      </c>
-      <c r="K101" s="24">
-        <v>3.9</v>
-      </c>
-      <c r="L101" s="24">
-        <v>15000</v>
-      </c>
-      <c r="M101" s="24">
-        <v>58500</v>
-      </c>
-      <c r="N101" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="O101" s="26">
-        <v>46261</v>
-      </c>
-      <c r="P101" s="26"/>
-      <c r="Q101" s="26"/>
-      <c r="R101" s="32"/>
-      <c r="T101" s="32">
-        <f ca="1" t="shared" si="28"/>
-        <v>2</v>
-      </c>
-      <c r="XET101" s="37"/>
-      <c r="XEU101" s="38"/>
-      <c r="XEV101" s="39"/>
-      <c r="XEW101" s="39"/>
-      <c r="XEX101" s="40"/>
-      <c r="XEY101" s="24"/>
-      <c r="XEZ101" s="25"/>
-      <c r="XFA101" s="26"/>
-      <c r="XFB101" s="26"/>
-      <c r="XFC101" s="24"/>
-      <c r="XFD101" s="25"/>
+    <row r="1048286" s="3" customFormat="1" customHeight="1" spans="3:22">
+      <c r="C1048286" s="5"/>
+      <c r="D1048286" s="5"/>
+      <c r="F1048286" s="6"/>
+      <c r="J1048286" s="5"/>
     </row>
-    <row r="102" s="1" customFormat="1" ht="14.1" customHeight="1" spans="1:25 16372:16384">
-      <c r="A102" s="24" t="s">
-        <v>309</v>
-      </c>
-      <c r="B102" s="25">
-        <v>46259</v>
-      </c>
-      <c r="C102" s="26">
-        <v>8110001692</v>
-      </c>
-      <c r="D102" s="26">
-        <v>46258</v>
-      </c>
-      <c r="E102" s="27" t="s">
-        <v>221</v>
-      </c>
-      <c r="F102" s="28" t="s">
-        <v>222</v>
-      </c>
-      <c r="G102" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="H102" s="29">
-        <v>1050730</v>
-      </c>
-      <c r="I102" s="29" t="s">
-        <v>310</v>
-      </c>
-      <c r="J102" s="24">
-        <v>48000</v>
-      </c>
-      <c r="K102" s="24">
-        <v>2.02</v>
-      </c>
-      <c r="L102" s="24">
-        <v>48000</v>
-      </c>
-      <c r="M102" s="24">
-        <v>96960</v>
-      </c>
-      <c r="N102" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="O102" s="26">
-        <v>46261</v>
-      </c>
-      <c r="P102" s="26"/>
-      <c r="Q102" s="26"/>
-      <c r="R102" s="32"/>
-      <c r="T102" s="32">
-        <f ca="1" t="shared" si="28"/>
-        <v>2</v>
-      </c>
-      <c r="XET102" s="37"/>
-      <c r="XEU102" s="38"/>
-      <c r="XEV102" s="39"/>
-      <c r="XEW102" s="39"/>
-      <c r="XEX102" s="40"/>
-      <c r="XEY102" s="24"/>
-      <c r="XEZ102" s="25"/>
-      <c r="XFA102" s="26"/>
-      <c r="XFB102" s="26"/>
-      <c r="XFC102" s="24"/>
-      <c r="XFD102" s="25"/>
+    <row r="1048287" s="3" customFormat="1" customHeight="1" spans="3:22">
+      <c r="C1048287" s="5"/>
+      <c r="D1048287" s="5"/>
+      <c r="F1048287" s="6"/>
+      <c r="J1048287" s="5"/>
     </row>
-    <row r="103" s="1" customFormat="1" ht="14.1" customHeight="1" spans="1:25 16372:16384">
-      <c r="A103" s="24" t="s">
-        <v>311</v>
-      </c>
-      <c r="B103" s="25">
-        <v>46259</v>
-      </c>
-      <c r="C103" s="26">
-        <v>8110001692</v>
-      </c>
-      <c r="D103" s="26">
-        <v>46258</v>
-      </c>
-      <c r="E103" s="27" t="s">
-        <v>221</v>
-      </c>
-      <c r="F103" s="28" t="s">
-        <v>222</v>
-      </c>
-      <c r="G103" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="H103" s="29">
-        <v>1050204</v>
-      </c>
-      <c r="I103" s="29" t="s">
-        <v>312</v>
-      </c>
-      <c r="J103" s="24">
-        <v>130000</v>
-      </c>
-      <c r="K103" s="24">
-        <v>1.58</v>
-      </c>
-      <c r="L103" s="24">
-        <v>130000</v>
-      </c>
-      <c r="M103" s="24">
-        <v>205400</v>
-      </c>
-      <c r="N103" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="O103" s="26">
-        <v>46261</v>
-      </c>
-      <c r="P103" s="26"/>
-      <c r="Q103" s="26"/>
-      <c r="R103" s="32"/>
-      <c r="T103" s="32">
-        <f ca="1" t="shared" si="28"/>
-        <v>2</v>
-      </c>
-      <c r="XET103" s="37"/>
-      <c r="XEU103" s="38"/>
-      <c r="XEV103" s="39"/>
-      <c r="XEW103" s="39"/>
-      <c r="XEX103" s="40"/>
-      <c r="XEY103" s="24"/>
-      <c r="XEZ103" s="25"/>
-      <c r="XFA103" s="26"/>
-      <c r="XFB103" s="26"/>
-      <c r="XFC103" s="24"/>
-      <c r="XFD103" s="25"/>
+    <row r="1048288" s="3" customFormat="1" customHeight="1" spans="3:22">
+      <c r="C1048288" s="5"/>
+      <c r="D1048288" s="5"/>
+      <c r="F1048288" s="6"/>
+      <c r="J1048288" s="5"/>
+      <c r="V1048288" s="19"/>
     </row>
-    <row r="104" s="1" customFormat="1" ht="14.1" customHeight="1" spans="1:25 16372:16384">
-      <c r="A104" s="24" t="s">
-        <v>313</v>
-      </c>
-      <c r="B104" s="25">
-        <v>46259</v>
-      </c>
-      <c r="C104" s="26">
-        <v>9500229040</v>
-      </c>
-      <c r="D104" s="26">
-        <v>46254</v>
-      </c>
-      <c r="E104" s="27" t="s">
-        <v>174</v>
-      </c>
-      <c r="F104" s="28" t="s">
-        <v>296</v>
-      </c>
-      <c r="G104" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="H104" s="29">
-        <v>2077975</v>
-      </c>
-      <c r="I104" s="29" t="s">
-        <v>314</v>
-      </c>
-      <c r="J104" s="24">
-        <v>22000</v>
-      </c>
-      <c r="K104" s="24">
-        <v>2.65</v>
-      </c>
-      <c r="L104" s="24">
-        <v>22000</v>
-      </c>
-      <c r="M104" s="24">
-        <v>58300</v>
-      </c>
-      <c r="N104" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="O104" s="26">
-        <v>46261</v>
-      </c>
-      <c r="P104" s="26"/>
-      <c r="Q104" s="26"/>
-      <c r="R104" s="32"/>
-      <c r="T104" s="32">
-        <f ca="1" t="shared" si="28"/>
-        <v>2</v>
-      </c>
-      <c r="XET104" s="37"/>
-      <c r="XEU104" s="38"/>
-      <c r="XEV104" s="39"/>
-      <c r="XEW104" s="39"/>
-      <c r="XEX104" s="40"/>
-      <c r="XEY104" s="24"/>
-      <c r="XEZ104" s="25"/>
-      <c r="XFA104" s="26"/>
-      <c r="XFB104" s="26"/>
-      <c r="XFC104" s="24"/>
-      <c r="XFD104" s="25"/>
+    <row r="1048289" s="3" customFormat="1" customHeight="1" spans="3:22">
+      <c r="C1048289" s="5"/>
+      <c r="D1048289" s="5"/>
+      <c r="F1048289" s="6"/>
+      <c r="J1048289" s="5"/>
+      <c r="V1048289" s="45"/>
     </row>
-    <row r="105" s="1" customFormat="1" ht="14.1" customHeight="1" spans="1:25 16372:16384">
-      <c r="A105" s="24" t="s">
-        <v>315</v>
-      </c>
-      <c r="B105" s="25">
-        <v>46259</v>
-      </c>
-      <c r="C105" s="26">
-        <v>4510017617</v>
-      </c>
-      <c r="D105" s="26">
-        <v>46254</v>
-      </c>
-      <c r="E105" s="27" t="s">
-        <v>263</v>
-      </c>
-      <c r="F105" s="28" t="s">
-        <v>316</v>
-      </c>
-      <c r="G105" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="H105" s="29">
-        <v>4200353</v>
-      </c>
-      <c r="I105" s="29" t="s">
-        <v>317</v>
-      </c>
-      <c r="J105" s="24">
-        <v>6300</v>
-      </c>
-      <c r="K105" s="24">
-        <v>2.98</v>
-      </c>
-      <c r="L105" s="24">
-        <v>6300</v>
-      </c>
-      <c r="M105" s="24">
-        <v>18774</v>
-      </c>
-      <c r="N105" s="26" t="s">
-        <v>249</v>
-      </c>
-      <c r="O105" s="26"/>
-      <c r="P105" s="26"/>
-      <c r="Q105" s="26"/>
-      <c r="R105" s="32"/>
-      <c r="T105" s="32">
-        <f ca="1" t="shared" si="28"/>
-        <v>2</v>
-      </c>
-      <c r="XET105" s="37"/>
-      <c r="XEU105" s="38"/>
-      <c r="XEV105" s="39"/>
-      <c r="XEW105" s="39"/>
-      <c r="XEX105" s="40"/>
-      <c r="XEY105" s="24"/>
-      <c r="XEZ105" s="25"/>
-      <c r="XFA105" s="26"/>
-      <c r="XFB105" s="26"/>
-      <c r="XFC105" s="24"/>
-      <c r="XFD105" s="25"/>
+    <row r="1048290" s="3" customFormat="1" customHeight="1" spans="3:22">
+      <c r="C1048290" s="5"/>
+      <c r="D1048290" s="5"/>
+      <c r="F1048290" s="6"/>
+      <c r="J1048290" s="5"/>
+      <c r="V1048290" s="45"/>
     </row>
-    <row r="106" s="1" customFormat="1" ht="14.1" customHeight="1" spans="1:25 16372:16384">
-      <c r="A106" s="24" t="s">
-        <v>318</v>
-      </c>
-      <c r="B106" s="25">
-        <v>46260</v>
-      </c>
-      <c r="C106" s="26">
-        <v>4300011676</v>
-      </c>
-      <c r="D106" s="26">
-        <v>46252</v>
-      </c>
-      <c r="E106" s="27" t="s">
-        <v>34</v>
-      </c>
-      <c r="F106" s="28" t="s">
-        <v>35</v>
-      </c>
-      <c r="G106" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="H106" s="29" t="s">
-        <v>319</v>
-      </c>
-      <c r="I106" s="29" t="s">
-        <v>320</v>
-      </c>
-      <c r="J106" s="24">
-        <v>12000</v>
-      </c>
-      <c r="K106" s="24">
-        <v>7.22</v>
-      </c>
-      <c r="L106" s="24">
-        <v>12000</v>
-      </c>
-      <c r="M106" s="24">
-        <v>86640</v>
-      </c>
-      <c r="N106" s="26" t="s">
-        <v>249</v>
-      </c>
-      <c r="O106" s="26"/>
-      <c r="P106" s="32"/>
-      <c r="R106" s="32"/>
-      <c r="T106" s="32">
-        <f ca="1" t="shared" si="28"/>
-        <v>1</v>
-      </c>
-      <c r="W106" s="1">
-        <v>3</v>
-      </c>
-      <c r="X106" s="1">
-        <v>4</v>
-      </c>
-      <c r="Y106" s="1">
-        <v>3</v>
-      </c>
-      <c r="XER106" s="37"/>
-      <c r="XES106" s="38"/>
-      <c r="XET106" s="39"/>
-      <c r="XEU106" s="39"/>
-      <c r="XEV106" s="40"/>
-      <c r="XEW106" s="24"/>
-      <c r="XEX106" s="25"/>
-      <c r="XEY106" s="26"/>
-      <c r="XEZ106" s="26"/>
-      <c r="XFA106" s="24"/>
-      <c r="XFB106" s="25"/>
-      <c r="XFC106" s="24"/>
-      <c r="XFD106" s="25"/>
+    <row r="1048291" s="3" customFormat="1" customHeight="1" spans="3:22">
+      <c r="C1048291" s="5"/>
+      <c r="D1048291" s="5"/>
+      <c r="F1048291" s="6"/>
+      <c r="J1048291" s="5"/>
+      <c r="V1048291" s="45"/>
     </row>
-    <row r="107" s="1" customFormat="1" ht="14.1" customHeight="1" spans="1:25 16372:16384">
-      <c r="A107" s="24" t="s">
-        <v>321</v>
-      </c>
-      <c r="B107" s="25">
-        <v>46260</v>
-      </c>
-      <c r="C107" s="26">
-        <v>4300011676</v>
-      </c>
-      <c r="D107" s="26">
-        <v>46252</v>
-      </c>
-      <c r="E107" s="27" t="s">
-        <v>34</v>
-      </c>
-      <c r="F107" s="28" t="s">
-        <v>35</v>
-      </c>
-      <c r="G107" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="H107" s="29" t="s">
-        <v>322</v>
-      </c>
-      <c r="I107" s="29" t="s">
-        <v>323</v>
-      </c>
-      <c r="J107" s="24">
-        <v>11000</v>
-      </c>
-      <c r="K107" s="24">
-        <v>4.65</v>
-      </c>
-      <c r="L107" s="24">
-        <v>11000</v>
-      </c>
-      <c r="M107" s="24">
-        <v>51150</v>
-      </c>
-      <c r="N107" s="26" t="s">
-        <v>249</v>
-      </c>
-      <c r="O107" s="26"/>
-      <c r="P107" s="32"/>
-      <c r="R107" s="32"/>
-      <c r="T107" s="32">
-        <f ca="1" t="shared" si="28"/>
-        <v>1</v>
-      </c>
-      <c r="XER107" s="37"/>
-      <c r="XES107" s="38"/>
-      <c r="XET107" s="39"/>
-      <c r="XEU107" s="39"/>
-      <c r="XEV107" s="40"/>
-      <c r="XEW107" s="24"/>
-      <c r="XEX107" s="25"/>
-      <c r="XEY107" s="26"/>
-      <c r="XEZ107" s="26"/>
-      <c r="XFA107" s="24"/>
-      <c r="XFB107" s="25"/>
-      <c r="XFC107" s="24"/>
-      <c r="XFD107" s="25"/>
+    <row r="1048292" s="3" customFormat="1" customHeight="1" spans="3:22">
+      <c r="C1048292" s="5"/>
+      <c r="D1048292" s="5"/>
+      <c r="F1048292" s="6"/>
+      <c r="J1048292" s="5"/>
+      <c r="V1048292" s="24"/>
     </row>
     <row r="1048293" s="3" customFormat="1" customHeight="1" spans="3:22">
       <c r="C1048293" s="5"/>
       <c r="D1048293" s="5"/>
       <c r="F1048293" s="6"/>
       <c r="J1048293" s="5"/>
+      <c r="V1048293" s="46"/>
     </row>
     <row r="1048294" s="3" customFormat="1" customHeight="1" spans="3:22">
       <c r="C1048294" s="5"/>
       <c r="D1048294" s="5"/>
       <c r="F1048294" s="6"/>
       <c r="J1048294" s="5"/>
+      <c r="V1048294" s="24"/>
     </row>
     <row r="1048295" s="3" customFormat="1" customHeight="1" spans="3:22">
       <c r="C1048295" s="5"/>
       <c r="D1048295" s="5"/>
       <c r="F1048295" s="6"/>
       <c r="J1048295" s="5"/>
-      <c r="V1048295" s="19"/>
+      <c r="V1048295" s="24"/>
     </row>
     <row r="1048296" s="3" customFormat="1" customHeight="1" spans="3:22">
       <c r="C1048296" s="5"/>
       <c r="D1048296" s="5"/>
       <c r="F1048296" s="6"/>
       <c r="J1048296" s="5"/>
-      <c r="V1048296" s="45"/>
+      <c r="V1048296" s="24"/>
     </row>
     <row r="1048297" s="3" customFormat="1" customHeight="1" spans="3:22">
       <c r="C1048297" s="5"/>
       <c r="D1048297" s="5"/>
       <c r="F1048297" s="6"/>
       <c r="J1048297" s="5"/>
-      <c r="V1048297" s="45"/>
+      <c r="V1048297" s="24"/>
     </row>
     <row r="1048298" s="3" customFormat="1" customHeight="1" spans="3:22">
       <c r="C1048298" s="5"/>
       <c r="D1048298" s="5"/>
       <c r="F1048298" s="6"/>
       <c r="J1048298" s="5"/>
-      <c r="V1048298" s="45"/>
+      <c r="V1048298" s="24"/>
     </row>
     <row r="1048299" s="3" customFormat="1" customHeight="1" spans="3:22">
       <c r="C1048299" s="5"/>
@@ -9969,7 +9498,7 @@
       <c r="D1048300" s="5"/>
       <c r="F1048300" s="6"/>
       <c r="J1048300" s="5"/>
-      <c r="V1048300" s="46"/>
+      <c r="V1048300" s="24"/>
     </row>
     <row r="1048301" s="3" customFormat="1" customHeight="1" spans="3:22">
       <c r="C1048301" s="5"/>
@@ -10151,49 +9680,42 @@
       <c r="D1048326" s="5"/>
       <c r="F1048326" s="6"/>
       <c r="J1048326" s="5"/>
-      <c r="V1048326" s="24"/>
     </row>
     <row r="1048327" s="3" customFormat="1" customHeight="1" spans="3:22">
       <c r="C1048327" s="5"/>
       <c r="D1048327" s="5"/>
       <c r="F1048327" s="6"/>
       <c r="J1048327" s="5"/>
-      <c r="V1048327" s="24"/>
     </row>
     <row r="1048328" s="3" customFormat="1" customHeight="1" spans="3:22">
       <c r="C1048328" s="5"/>
       <c r="D1048328" s="5"/>
       <c r="F1048328" s="6"/>
       <c r="J1048328" s="5"/>
-      <c r="V1048328" s="24"/>
     </row>
     <row r="1048329" s="3" customFormat="1" customHeight="1" spans="3:22">
       <c r="C1048329" s="5"/>
       <c r="D1048329" s="5"/>
       <c r="F1048329" s="6"/>
       <c r="J1048329" s="5"/>
-      <c r="V1048329" s="24"/>
     </row>
     <row r="1048330" s="3" customFormat="1" customHeight="1" spans="3:22">
       <c r="C1048330" s="5"/>
       <c r="D1048330" s="5"/>
       <c r="F1048330" s="6"/>
       <c r="J1048330" s="5"/>
-      <c r="V1048330" s="24"/>
     </row>
     <row r="1048331" s="3" customFormat="1" customHeight="1" spans="3:22">
       <c r="C1048331" s="5"/>
       <c r="D1048331" s="5"/>
       <c r="F1048331" s="6"/>
       <c r="J1048331" s="5"/>
-      <c r="V1048331" s="24"/>
     </row>
     <row r="1048332" s="3" customFormat="1" customHeight="1" spans="3:22">
       <c r="C1048332" s="5"/>
       <c r="D1048332" s="5"/>
       <c r="F1048332" s="6"/>
       <c r="J1048332" s="5"/>
-      <c r="V1048332" s="24"/>
     </row>
     <row r="1048333" s="3" customFormat="1" customHeight="1" spans="3:22">
       <c r="C1048333" s="5"/>
@@ -10447,50 +9969,8 @@
       <c r="F1048374" s="6"/>
       <c r="J1048374" s="5"/>
     </row>
-    <row r="1048375" s="3" customFormat="1" customHeight="1" spans="3:10">
-      <c r="C1048375" s="5"/>
-      <c r="D1048375" s="5"/>
-      <c r="F1048375" s="6"/>
-      <c r="J1048375" s="5"/>
-    </row>
-    <row r="1048376" s="3" customFormat="1" customHeight="1" spans="3:10">
-      <c r="C1048376" s="5"/>
-      <c r="D1048376" s="5"/>
-      <c r="F1048376" s="6"/>
-      <c r="J1048376" s="5"/>
-    </row>
-    <row r="1048377" s="3" customFormat="1" customHeight="1" spans="3:10">
-      <c r="C1048377" s="5"/>
-      <c r="D1048377" s="5"/>
-      <c r="F1048377" s="6"/>
-      <c r="J1048377" s="5"/>
-    </row>
-    <row r="1048378" s="3" customFormat="1" customHeight="1" spans="3:10">
-      <c r="C1048378" s="5"/>
-      <c r="D1048378" s="5"/>
-      <c r="F1048378" s="6"/>
-      <c r="J1048378" s="5"/>
-    </row>
-    <row r="1048379" s="3" customFormat="1" customHeight="1" spans="3:10">
-      <c r="C1048379" s="5"/>
-      <c r="D1048379" s="5"/>
-      <c r="F1048379" s="6"/>
-      <c r="J1048379" s="5"/>
-    </row>
-    <row r="1048380" s="3" customFormat="1" customHeight="1" spans="3:10">
-      <c r="C1048380" s="5"/>
-      <c r="D1048380" s="5"/>
-      <c r="F1048380" s="6"/>
-      <c r="J1048380" s="5"/>
-    </row>
-    <row r="1048381" s="3" customFormat="1" customHeight="1" spans="3:10">
-      <c r="C1048381" s="5"/>
-      <c r="D1048381" s="5"/>
-      <c r="F1048381" s="6"/>
-      <c r="J1048381" s="5"/>
-    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A3:XFD107" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A3:XFD100" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <mergeCells count="1">
@@ -20712,823 +20192,7 @@
   <conditionalFormatting sqref="XFC100">
     <cfRule type="duplicateValues" dxfId="0" priority="775"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A101">
-    <cfRule type="duplicateValues" dxfId="0" priority="774"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H101">
-    <cfRule type="duplicateValues" dxfId="0" priority="783"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="790"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="797"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="804"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="811"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="818"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="825"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="832"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="839"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="846"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="853"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="860"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="867"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="874"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="881"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="888"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="895"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="902"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="909"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="916"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J101">
-    <cfRule type="duplicateValues" dxfId="0" priority="615"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="622"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="629"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="636"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="643"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="650"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="657"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="664"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="671"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="678"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="685"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="692"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="699"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="706"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="713"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="720"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="727"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="734"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="741"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="748"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K101">
-    <cfRule type="duplicateValues" dxfId="0" priority="475"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="482"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="489"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="496"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="503"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="510"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="517"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="524"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="531"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="538"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="545"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="552"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="559"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="566"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="573"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="580"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="587"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="594"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="601"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="608"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L101">
-    <cfRule type="duplicateValues" dxfId="0" priority="195"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="202"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="209"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="216"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="223"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="230"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="237"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="244"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="251"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="258"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="265"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="272"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="279"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="286"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="293"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="300"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="307"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="314"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="321"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="328"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M101">
-    <cfRule type="duplicateValues" dxfId="0" priority="335"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="342"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="349"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="356"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="363"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="370"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="377"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="384"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="391"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="398"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="405"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="412"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="419"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="426"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="433"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="440"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="447"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="454"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="461"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="468"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="XET101">
-    <cfRule type="duplicateValues" dxfId="0" priority="755"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="XEY101">
-    <cfRule type="duplicateValues" dxfId="0" priority="762"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="XFC101">
-    <cfRule type="duplicateValues" dxfId="0" priority="773"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A102">
-    <cfRule type="duplicateValues" dxfId="0" priority="772"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H102">
-    <cfRule type="duplicateValues" dxfId="0" priority="782"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="789"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="796"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="803"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="810"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="817"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="824"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="831"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="838"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="845"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="852"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="859"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="866"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="873"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="880"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="887"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="894"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="901"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="908"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="915"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J102">
-    <cfRule type="duplicateValues" dxfId="0" priority="614"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="621"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="628"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="635"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="642"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="649"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="656"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="663"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="670"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="677"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="684"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="691"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="698"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="705"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="712"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="719"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="726"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="733"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="740"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="747"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K102">
-    <cfRule type="duplicateValues" dxfId="0" priority="474"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="481"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="488"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="495"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="502"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="509"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="516"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="523"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="530"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="537"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="544"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="551"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="558"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="565"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="572"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="579"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="586"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="593"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="600"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="607"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L102">
-    <cfRule type="duplicateValues" dxfId="0" priority="194"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="201"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="208"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="215"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="222"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="229"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="236"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="243"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="250"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="257"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="264"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="271"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="278"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="285"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="292"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="299"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="306"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="313"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="320"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="327"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M102">
-    <cfRule type="duplicateValues" dxfId="0" priority="334"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="341"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="348"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="355"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="362"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="369"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="376"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="383"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="390"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="397"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="404"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="411"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="418"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="425"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="432"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="439"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="446"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="453"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="460"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="467"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="XET102">
-    <cfRule type="duplicateValues" dxfId="0" priority="754"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="XEY102">
-    <cfRule type="duplicateValues" dxfId="0" priority="761"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="XFC102">
-    <cfRule type="duplicateValues" dxfId="0" priority="771"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A103">
-    <cfRule type="duplicateValues" dxfId="0" priority="770"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H103">
-    <cfRule type="duplicateValues" dxfId="0" priority="781"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="788"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="795"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="802"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="809"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="816"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="823"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="830"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="837"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="844"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="851"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="858"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="865"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="872"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="879"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="886"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="893"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="900"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="907"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="914"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J103">
-    <cfRule type="duplicateValues" dxfId="0" priority="613"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="620"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="627"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="634"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="641"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="648"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="655"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="662"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="669"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="676"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="683"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="690"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="697"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="704"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="711"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="718"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="725"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="732"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="739"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="746"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K103">
-    <cfRule type="duplicateValues" dxfId="0" priority="473"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="480"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="487"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="494"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="501"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="508"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="515"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="522"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="529"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="536"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="543"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="550"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="557"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="564"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="571"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="578"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="585"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="592"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="599"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="606"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L103">
-    <cfRule type="duplicateValues" dxfId="0" priority="193"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="200"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="207"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="214"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="221"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="228"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="235"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="242"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="249"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="256"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="263"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="270"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="277"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="284"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="291"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="298"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="305"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="312"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="319"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="326"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M103">
-    <cfRule type="duplicateValues" dxfId="0" priority="333"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="340"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="347"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="354"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="361"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="368"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="375"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="382"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="389"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="396"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="403"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="410"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="417"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="424"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="431"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="438"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="445"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="452"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="459"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="466"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="XET103">
-    <cfRule type="duplicateValues" dxfId="0" priority="753"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="XEY103">
-    <cfRule type="duplicateValues" dxfId="0" priority="760"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="XFC103">
-    <cfRule type="duplicateValues" dxfId="0" priority="769"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A104">
-    <cfRule type="duplicateValues" dxfId="0" priority="768"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H104">
-    <cfRule type="duplicateValues" dxfId="0" priority="780"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="787"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="794"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="801"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="808"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="815"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="822"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="829"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="836"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="843"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="850"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="857"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="864"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="871"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="878"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="885"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="892"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="899"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="906"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="913"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J104">
-    <cfRule type="duplicateValues" dxfId="0" priority="612"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="619"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="626"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="633"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="640"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="647"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="654"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="661"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="668"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="675"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="682"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="689"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="696"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="703"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="710"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="717"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="724"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="731"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="738"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="745"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K104">
-    <cfRule type="duplicateValues" dxfId="0" priority="472"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="479"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="486"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="493"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="500"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="507"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="514"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="521"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="528"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="535"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="542"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="549"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="556"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="563"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="570"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="577"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="584"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="591"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="598"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="605"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L104">
-    <cfRule type="duplicateValues" dxfId="0" priority="192"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="199"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="206"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="213"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="220"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="227"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="234"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="241"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="248"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="255"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="262"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="269"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="276"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="283"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="290"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="297"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="304"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="311"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="318"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="325"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M104">
-    <cfRule type="duplicateValues" dxfId="0" priority="332"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="339"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="346"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="353"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="360"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="367"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="374"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="381"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="388"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="395"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="402"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="409"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="416"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="423"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="430"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="437"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="444"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="451"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="458"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="465"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="XET104">
-    <cfRule type="duplicateValues" dxfId="0" priority="752"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="XEY104">
-    <cfRule type="duplicateValues" dxfId="0" priority="759"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="XFC104">
-    <cfRule type="duplicateValues" dxfId="0" priority="767"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A105">
-    <cfRule type="duplicateValues" dxfId="0" priority="766"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H105">
-    <cfRule type="duplicateValues" dxfId="0" priority="779"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="786"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="793"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="800"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="807"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="814"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="821"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="828"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="835"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="842"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="849"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="856"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="863"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="870"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="877"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="884"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="891"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="898"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="905"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="912"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J105">
-    <cfRule type="duplicateValues" dxfId="0" priority="611"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="618"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="625"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="632"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="639"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="646"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="653"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="660"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="667"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="674"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="681"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="688"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="695"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="702"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="709"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="716"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="723"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="730"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="737"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="744"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K105">
-    <cfRule type="duplicateValues" dxfId="0" priority="471"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="478"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="485"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="492"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="499"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="506"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="513"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="520"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="527"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="534"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="541"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="548"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="555"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="562"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="569"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="576"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="583"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="590"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="597"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="604"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L105">
-    <cfRule type="duplicateValues" dxfId="0" priority="191"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="198"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="205"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="212"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="219"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="226"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="233"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="240"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="247"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="254"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="261"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="268"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="275"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="282"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="289"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="296"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="303"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="310"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="317"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="324"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M105">
-    <cfRule type="duplicateValues" dxfId="0" priority="331"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="338"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="345"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="352"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="359"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="366"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="373"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="380"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="387"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="394"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="401"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="408"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="415"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="422"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="429"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="436"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="443"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="450"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="457"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="464"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="XET105">
-    <cfRule type="duplicateValues" dxfId="0" priority="751"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="XEY105">
-    <cfRule type="duplicateValues" dxfId="0" priority="758"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="XFC105">
-    <cfRule type="duplicateValues" dxfId="0" priority="765"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A106">
-    <cfRule type="duplicateValues" dxfId="0" priority="150"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H106">
-    <cfRule type="duplicateValues" dxfId="0" priority="152"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="154"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="156"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="158"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="160"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="162"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="164"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="166"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="168"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="170"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="172"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="174"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="176"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="178"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="180"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="182"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="184"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="186"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="188"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="190"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J106">
-    <cfRule type="duplicateValues" dxfId="0" priority="102"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="104"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="106"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="108"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="110"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="112"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="114"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="116"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="118"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="120"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="122"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="124"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="126"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="128"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="130"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="132"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="134"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="136"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="138"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="140"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K106">
-    <cfRule type="duplicateValues" dxfId="0" priority="62"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="64"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="66"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="68"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="70"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="72"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="74"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="76"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="78"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="80"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="82"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="84"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="86"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="88"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="90"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="92"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="94"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="96"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="98"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="100"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L106">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="22"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="24"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="26"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="28"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="30"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="32"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="34"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="36"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="38"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="40"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="XER106">
-    <cfRule type="duplicateValues" dxfId="0" priority="142"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="XEW106">
-    <cfRule type="duplicateValues" dxfId="0" priority="144"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="XFA106">
-    <cfRule type="duplicateValues" dxfId="0" priority="146"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="XFC106">
-    <cfRule type="duplicateValues" dxfId="0" priority="149"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A107">
-    <cfRule type="duplicateValues" dxfId="0" priority="148"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H107">
-    <cfRule type="duplicateValues" dxfId="0" priority="151"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="153"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="155"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="157"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="159"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="161"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="163"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="165"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="167"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="169"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="171"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="173"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="175"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="177"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="179"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="181"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="183"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="185"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="187"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="189"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J107">
-    <cfRule type="duplicateValues" dxfId="0" priority="101"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="103"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="105"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="107"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="109"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="111"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="113"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="115"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="117"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="119"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="121"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="123"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="125"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="127"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="129"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="131"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="133"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="135"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="137"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="139"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K107">
-    <cfRule type="duplicateValues" dxfId="0" priority="61"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="63"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="65"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="67"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="69"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="71"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="73"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="75"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="77"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="79"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="81"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="83"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="85"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="87"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="89"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="91"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="93"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="95"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="97"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="99"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L107">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="27"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="29"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="31"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="33"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="35"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="37"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="39"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="XER107">
-    <cfRule type="duplicateValues" dxfId="0" priority="141"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="XEW107">
-    <cfRule type="duplicateValues" dxfId="0" priority="143"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="XFA107">
-    <cfRule type="duplicateValues" dxfId="0" priority="145"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="XFC107">
-    <cfRule type="duplicateValues" dxfId="0" priority="147"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V1048296">
+  <conditionalFormatting sqref="V1048289">
     <cfRule type="duplicateValues" dxfId="0" priority="9358"/>
     <cfRule type="duplicateValues" dxfId="0" priority="9359"/>
     <cfRule type="duplicateValues" dxfId="0" priority="9360"/>
@@ -21550,7 +20214,7 @@
     <cfRule type="duplicateValues" dxfId="0" priority="9376"/>
     <cfRule type="duplicateValues" dxfId="0" priority="9377"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V1048297">
+  <conditionalFormatting sqref="V1048290">
     <cfRule type="duplicateValues" dxfId="0" priority="9338"/>
     <cfRule type="duplicateValues" dxfId="0" priority="9339"/>
     <cfRule type="duplicateValues" dxfId="0" priority="9340"/>
@@ -21572,7 +20236,7 @@
     <cfRule type="duplicateValues" dxfId="0" priority="9356"/>
     <cfRule type="duplicateValues" dxfId="0" priority="9357"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V1048298">
+  <conditionalFormatting sqref="V1048291">
     <cfRule type="duplicateValues" dxfId="0" priority="9298"/>
     <cfRule type="duplicateValues" dxfId="0" priority="9300"/>
     <cfRule type="duplicateValues" dxfId="0" priority="9302"/>
@@ -21594,32 +20258,10 @@
     <cfRule type="duplicateValues" dxfId="0" priority="9334"/>
     <cfRule type="duplicateValues" dxfId="0" priority="9336"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M106:M107">
-    <cfRule type="duplicateValues" dxfId="0" priority="41"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="42"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="43"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="44"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="45"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="46"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="47"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="48"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="49"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="50"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="51"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="52"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="53"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="54"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="55"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="56"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="57"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="58"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="59"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="60"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A3 A108:A1048576">
+  <conditionalFormatting sqref="A1:A3 A101:A1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="10938"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H1:H3 G108:G1048576">
+  <conditionalFormatting sqref="H1:H3 G101:G1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="10884"/>
     <cfRule type="duplicateValues" dxfId="0" priority="10925"/>
     <cfRule type="duplicateValues" dxfId="0" priority="10926"/>

--- a/data/pending_orders.xlsx
+++ b/data/pending_orders.xlsx
@@ -7,10 +7,10 @@
     <workbookView windowWidth="19635" windowHeight="7500"/>
   </bookViews>
   <sheets>
-    <sheet name="Actual pending as on today (2)" sheetId="28" r:id="rId1"/>
+    <sheet name="Actual pending as on today" sheetId="29" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Actual pending as on today (2)'!$3:$98</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Actual pending as on today'!$3:$98</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -2407,8 +2407,8 @@
     <col min="7" max="7" width="10.4285714285714" style="3" customWidth="1"/>
     <col min="8" max="8" width="13.4285714285714" style="3" customWidth="1"/>
     <col min="9" max="9" width="56.7333333333333" style="4" customWidth="1"/>
-    <col min="10" max="10" width="11.8571428571429" style="5" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="9.57142857142857" style="3" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="11.8571428571429" style="5" customWidth="1"/>
+    <col min="11" max="11" width="9.57142857142857" style="3" customWidth="1"/>
     <col min="12" max="17" width="12.8571428571429" style="3" customWidth="1"/>
     <col min="18" max="18" width="11.1428571428571" style="3" hidden="1" customWidth="1"/>
     <col min="19" max="19" width="12.0380952380952" style="3" hidden="1" customWidth="1"/>
@@ -8796,9 +8796,11 @@
         <v>56298.9</v>
       </c>
       <c r="N92" s="45" t="s">
-        <v>273</v>
-      </c>
-      <c r="O92" s="45"/>
+        <v>71</v>
+      </c>
+      <c r="O92" s="45">
+        <v>46265</v>
+      </c>
       <c r="P92" s="28"/>
       <c r="R92" s="28"/>
       <c r="S92" s="49">
@@ -9068,9 +9070,11 @@
         <v>53550</v>
       </c>
       <c r="N96" s="45" t="s">
-        <v>273</v>
-      </c>
-      <c r="O96" s="45"/>
+        <v>71</v>
+      </c>
+      <c r="O96" s="45">
+        <v>46265</v>
+      </c>
       <c r="Q96" s="28"/>
       <c r="T96" s="28">
         <f ca="1" t="shared" si="21"/>
@@ -9134,9 +9138,11 @@
         <v>20700</v>
       </c>
       <c r="N97" s="45" t="s">
-        <v>273</v>
-      </c>
-      <c r="O97" s="45"/>
+        <v>71</v>
+      </c>
+      <c r="O97" s="45">
+        <v>46265</v>
+      </c>
       <c r="Q97" s="28"/>
       <c r="T97" s="28">
         <f ca="1" t="shared" si="21"/>
